--- a/Jeonse_results3.xlsx
+++ b/Jeonse_results3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Senior Thesis Excel Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5B0FE8-3662-491C-B0DF-7D087C3814A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC2F4F4-90E9-4FA7-B83A-02AF4BDBCA9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,15 +44,6 @@
   </si>
   <si>
     <t>const</t>
-  </si>
-  <si>
-    <t>event_-9</t>
-  </si>
-  <si>
-    <t>event_-8</t>
-  </si>
-  <si>
-    <t>event_-7</t>
   </si>
   <si>
     <t>event_-6</t>
@@ -98,6 +89,15 @@
   </si>
   <si>
     <t>event_9</t>
+  </si>
+  <si>
+    <t>event_10</t>
+  </si>
+  <si>
+    <t>event_11</t>
+  </si>
+  <si>
+    <t>event_12</t>
   </si>
   <si>
     <t>ratio_lag1</t>
@@ -254,58 +254,58 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>1.5400868233533269E-3</c:v>
+                  <c:v>1.7763194432534189E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0770307358409089E-3</c:v>
+                  <c:v>1.92405804597854E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.93815799458386E-3</c:v>
+                  <c:v>2.660778030934223E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-9.6883126129203127E-4</c:v>
+                  <c:v>3.248024905077931E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.3379857040612091E-4</c:v>
+                  <c:v>3.135362357840607E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.1244981219933507E-4</c:v>
+                  <c:v>7.5978850087212576E-3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.9830570590065425E-4</c:v>
+                  <c:v>4.0551746995712984E-3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1.55848553796248E-3</c:v>
+                  <c:v>5.5006374770258937E-3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9.8801497931128154E-4</c:v>
+                  <c:v>2.9436682961950789E-3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-2.1866961131111109E-3</c:v>
+                  <c:v>9.3327498300428691E-3</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.142430593663625E-3</c:v>
+                  <c:v>9.1893735175041513E-3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1.787382394893961E-3</c:v>
+                  <c:v>-6.3797080666784939E-3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.9654085890260429E-3</c:v>
+                  <c:v>6.4531799014029556E-4</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>5.0368314322746252E-3</c:v>
+                  <c:v>4.0813231550054091E-3</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-8.2552097262090229E-3</c:v>
+                  <c:v>2.8505618449091719E-3</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2.1061969550504409E-3</c:v>
+                  <c:v>3.9668080992002058E-3</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-4.1282459149529719E-5</c:v>
+                  <c:v>6.454151646594769E-4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-6.6116470924782833E-4</c:v>
+                  <c:v>2.0052375797639239E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -313,7 +313,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-33B9-431C-A7F9-97BA003EBA1A}"/>
+              <c16:uniqueId val="{00000000-B2DB-4FE5-B083-9F98CA51A745}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -326,11 +326,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1676751375"/>
-        <c:axId val="1676752335"/>
+        <c:axId val="2101729424"/>
+        <c:axId val="2101727504"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1676751375"/>
+        <c:axId val="2101729424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -372,7 +372,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1676752335"/>
+        <c:crossAx val="2101727504"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -380,7 +380,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1676752335"/>
+        <c:axId val="2101727504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -431,7 +431,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1676751375"/>
+        <c:crossAx val="2101729424"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1047,23 +1047,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>130175</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>593725</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>434975</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:colOff>288925</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3DAD55D-3C7D-A8BE-DADF-C156D4913E5B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B68DB755-2BF3-0F10-A7A2-893F1081D756}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1397,22 +1397,22 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>-2.5502982159885312E-4</v>
+        <v>9.9551630605241928E-3</v>
       </c>
       <c r="C2">
-        <v>7.1891636757137601E-4</v>
+        <v>1.3662639787517991E-2</v>
       </c>
       <c r="D2">
-        <v>-0.35474198822373182</v>
+        <v>0.72864125932816437</v>
       </c>
       <c r="E2">
-        <v>0.72278289196249224</v>
+        <v>0.46622113316384128</v>
       </c>
       <c r="F2">
-        <v>-1.664080009935109E-3</v>
+        <v>-1.682311885675505E-2</v>
       </c>
       <c r="G2">
-        <v>1.154020366737403E-3</v>
+        <v>3.6733444977803432E-2</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -1420,22 +1420,22 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>1.5400868233533269E-3</v>
+        <v>1.7763194432534189E-3</v>
       </c>
       <c r="C3">
-        <v>2.5052273818251602E-4</v>
+        <v>5.2373248182886138E-3</v>
       </c>
       <c r="D3">
-        <v>6.1474931757743736</v>
+        <v>0.33916541457397359</v>
       </c>
       <c r="E3">
-        <v>7.8717085773283596E-10</v>
+        <v>0.73448512189061654</v>
       </c>
       <c r="F3">
-        <v>1.049071279207238E-3</v>
+        <v>-8.4886485759300481E-3</v>
       </c>
       <c r="G3">
-        <v>2.0311023674994158E-3</v>
+        <v>1.204128746243689E-2</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -1443,22 +1443,22 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>1.0770307358409089E-3</v>
+        <v>1.92405804597854E-3</v>
       </c>
       <c r="C4">
-        <v>2.465561124884968E-4</v>
+        <v>3.97325501836271E-3</v>
       </c>
       <c r="D4">
-        <v>4.368298660172778</v>
+        <v>0.48425234148987528</v>
       </c>
       <c r="E4">
-        <v>1.252181806719251E-5</v>
+        <v>0.62820679445313909</v>
       </c>
       <c r="F4">
-        <v>5.9378963519524943E-4</v>
+        <v>-5.8633786914054032E-3</v>
       </c>
       <c r="G4">
-        <v>1.560271836486569E-3</v>
+        <v>9.7114947833624836E-3</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -1466,22 +1466,22 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>3.93815799458386E-3</v>
+        <v>2.660778030934223E-3</v>
       </c>
       <c r="C5">
-        <v>1.2753355157979181E-3</v>
+        <v>3.5860696294553311E-3</v>
       </c>
       <c r="D5">
-        <v>3.0879387783064591</v>
+        <v>0.74197612034051741</v>
       </c>
       <c r="E5">
-        <v>2.015499879318137E-3</v>
+        <v>0.4581018039280822</v>
       </c>
       <c r="F5">
-        <v>1.438546315415128E-3</v>
+        <v>-4.3677892888511222E-3</v>
       </c>
       <c r="G5">
-        <v>6.4377696737525913E-3</v>
+        <v>9.6893453507195682E-3</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -1489,22 +1489,22 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>-9.6883126129203127E-4</v>
+        <v>3.248024905077931E-3</v>
       </c>
       <c r="C6">
-        <v>1.686621125188491E-3</v>
+        <v>3.300077333549375E-3</v>
       </c>
       <c r="D6">
-        <v>-0.57442139602262943</v>
+        <v>0.98422690645995903</v>
       </c>
       <c r="E6">
-        <v>0.56568267768182934</v>
+        <v>0.32500395911514368</v>
       </c>
       <c r="F6">
-        <v>-4.2745479222258964E-3</v>
+        <v>-3.220007814875817E-3</v>
       </c>
       <c r="G6">
-        <v>2.3368853996418339E-3</v>
+        <v>9.7160576250316794E-3</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -1512,22 +1512,22 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>1.3379857040612091E-4</v>
+        <v>3.135362357840607E-3</v>
       </c>
       <c r="C7">
-        <v>1.706417028610847E-3</v>
+        <v>3.8307693880177168E-3</v>
       </c>
       <c r="D7">
-        <v>7.840906892205772E-2</v>
+        <v>0.81846805178294546</v>
       </c>
       <c r="E7">
-        <v>0.93750265978612646</v>
+        <v>0.41308997747423498</v>
       </c>
       <c r="F7">
-        <v>-3.210717348276995E-3</v>
+        <v>-4.3728076757526624E-3</v>
       </c>
       <c r="G7">
-        <v>3.4783144890892358E-3</v>
+        <v>1.0643532391433881E-2</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -1535,22 +1535,22 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>6.1244981219933507E-4</v>
+        <v>7.5978850087212576E-3</v>
       </c>
       <c r="C8">
-        <v>2.071790960835151E-3</v>
+        <v>2.769252703464703E-3</v>
       </c>
       <c r="D8">
-        <v>0.29561370996254038</v>
+        <v>2.7436589659063242</v>
       </c>
       <c r="E8">
-        <v>0.76752510231754534</v>
+        <v>6.0758622482508136E-3</v>
       </c>
       <c r="F8">
-        <v>-3.4481858545331941E-3</v>
+        <v>2.1702494458402631E-3</v>
       </c>
       <c r="G8">
-        <v>4.6730854789318634E-3</v>
+        <v>1.302552057160225E-2</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
@@ -1558,22 +1558,22 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>7.9830570590065425E-4</v>
+        <v>4.0551746995712984E-3</v>
       </c>
       <c r="C9">
-        <v>1.9545529693804119E-3</v>
+        <v>2.832826250410527E-3</v>
       </c>
       <c r="D9">
-        <v>0.40843390709115179</v>
+        <v>1.4314943244343461</v>
       </c>
       <c r="E9">
-        <v>0.68295514430527615</v>
+        <v>0.15228859243241691</v>
       </c>
       <c r="F9">
-        <v>-3.0325477199607729E-3</v>
+        <v>-1.497062725692979E-3</v>
       </c>
       <c r="G9">
-        <v>4.6291591317620812E-3</v>
+        <v>9.6074121248355751E-3</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -1581,22 +1581,22 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>-1.55848553796248E-3</v>
+        <v>5.5006374770258937E-3</v>
       </c>
       <c r="C10">
-        <v>4.4281910456921121E-3</v>
+        <v>3.328905792295677E-3</v>
       </c>
       <c r="D10">
-        <v>-0.35194631891020722</v>
+        <v>1.6523860452153409</v>
       </c>
       <c r="E10">
-        <v>0.72487852120570628</v>
+        <v>9.845587845782483E-2</v>
       </c>
       <c r="F10">
-        <v>-1.0237580504181779E-2</v>
+        <v>-1.0238979838004059E-3</v>
       </c>
       <c r="G10">
-        <v>7.1206094282568206E-3</v>
+        <v>1.2025172937852191E-2</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -1604,22 +1604,22 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>9.8801497931128154E-4</v>
+        <v>2.9436682961950789E-3</v>
       </c>
       <c r="C11">
-        <v>2.3326036686593678E-3</v>
+        <v>2.9643260582152111E-3</v>
       </c>
       <c r="D11">
-        <v>0.42356744636311477</v>
+        <v>0.99303121127215999</v>
       </c>
       <c r="E11">
-        <v>0.6718813006604234</v>
+        <v>0.32069474455287911</v>
       </c>
       <c r="F11">
-        <v>-3.5838042014670812E-3</v>
+        <v>-2.8663040163403189E-3</v>
       </c>
       <c r="G11">
-        <v>5.5598341600896443E-3</v>
+        <v>8.7536406087304758E-3</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -1627,22 +1627,22 @@
         <v>16</v>
       </c>
       <c r="B12">
-        <v>-2.1866961131111109E-3</v>
+        <v>9.3327498300428691E-3</v>
       </c>
       <c r="C12">
-        <v>3.7524203468722209E-3</v>
+        <v>1.8507016242941592E-2</v>
       </c>
       <c r="D12">
-        <v>-0.58274284620959427</v>
+        <v>0.5042817117320193</v>
       </c>
       <c r="E12">
-        <v>0.56006642514287786</v>
+        <v>0.61406342708388206</v>
       </c>
       <c r="F12">
-        <v>-9.5413048478359616E-3</v>
+        <v>-2.6940335467420421E-2</v>
       </c>
       <c r="G12">
-        <v>5.167912621613739E-3</v>
+        <v>4.5605835127506163E-2</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -1650,22 +1650,22 @@
         <v>17</v>
       </c>
       <c r="B13">
-        <v>1.142430593663625E-3</v>
+        <v>9.1893735175041513E-3</v>
       </c>
       <c r="C13">
-        <v>2.750068390335373E-3</v>
+        <v>7.6022903969374259E-3</v>
       </c>
       <c r="D13">
-        <v>0.41541897564384023</v>
+        <v>1.208763811654193</v>
       </c>
       <c r="E13">
-        <v>0.67783521787564927</v>
+        <v>0.2267535982824429</v>
       </c>
       <c r="F13">
-        <v>-4.2476044064157443E-3</v>
+        <v>-5.7108418605079144E-3</v>
       </c>
       <c r="G13">
-        <v>6.5324655937429943E-3</v>
+        <v>2.4089588895516219E-2</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -1673,22 +1673,22 @@
         <v>18</v>
       </c>
       <c r="B14">
-        <v>-1.787382394893961E-3</v>
+        <v>-6.3797080666784939E-3</v>
       </c>
       <c r="C14">
-        <v>2.8310144303862082E-3</v>
+        <v>4.2983312416624061E-3</v>
       </c>
       <c r="D14">
-        <v>-0.63135757123291147</v>
+        <v>-1.4842290433184719</v>
       </c>
       <c r="E14">
-        <v>0.52780675158863444</v>
+        <v>0.13774816726425501</v>
       </c>
       <c r="F14">
-        <v>-7.336068718164104E-3</v>
+        <v>-1.480428249396014E-2</v>
       </c>
       <c r="G14">
-        <v>3.761303928376182E-3</v>
+        <v>2.0448663606031539E-3</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
@@ -1696,22 +1696,22 @@
         <v>19</v>
       </c>
       <c r="B15">
-        <v>1.9654085890260429E-3</v>
+        <v>6.4531799014029556E-4</v>
       </c>
       <c r="C15">
-        <v>1.428766327559527E-2</v>
+        <v>3.6705310970014302E-3</v>
       </c>
       <c r="D15">
-        <v>0.13755983404110281</v>
+        <v>0.17581052253377599</v>
       </c>
       <c r="E15">
-        <v>0.89058830145384427</v>
+        <v>0.86044280261850736</v>
       </c>
       <c r="F15">
-        <v>-2.6037896854376259E-2</v>
+        <v>-6.5487907641168016E-3</v>
       </c>
       <c r="G15">
-        <v>2.9968714032428342E-2</v>
+        <v>7.8394267443973945E-3</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
@@ -1719,22 +1719,22 @@
         <v>20</v>
       </c>
       <c r="B16">
-        <v>5.0368314322746252E-3</v>
+        <v>4.0813231550054091E-3</v>
       </c>
       <c r="C16">
-        <v>4.3497605280272723E-3</v>
+        <v>3.6368990387296439E-3</v>
       </c>
       <c r="D16">
-        <v>1.1579560299515981</v>
+        <v>1.1221986399795689</v>
       </c>
       <c r="E16">
-        <v>0.24688198050376869</v>
+        <v>0.26177799078123332</v>
       </c>
       <c r="F16">
-        <v>-3.4885425440327562E-3</v>
+        <v>-3.046867976313036E-3</v>
       </c>
       <c r="G16">
-        <v>1.3562205408582009E-2</v>
+        <v>1.120951428632385E-2</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -1742,22 +1742,22 @@
         <v>21</v>
       </c>
       <c r="B17">
-        <v>-8.2552097262090229E-3</v>
+        <v>2.8505618449091719E-3</v>
       </c>
       <c r="C17">
-        <v>7.5277487776684816E-3</v>
+        <v>3.4032920695739252E-3</v>
       </c>
       <c r="D17">
-        <v>-1.0966372510595199</v>
+        <v>0.83758954172453615</v>
       </c>
       <c r="E17">
-        <v>0.27279999666200738</v>
+        <v>0.40226126851442279</v>
       </c>
       <c r="F17">
-        <v>-2.300932621510466E-2</v>
+        <v>-3.819768040326505E-3</v>
       </c>
       <c r="G17">
-        <v>6.4989067626866157E-3</v>
+        <v>9.5208917301448474E-3</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -1765,22 +1765,22 @@
         <v>22</v>
       </c>
       <c r="B18">
-        <v>2.1061969550504409E-3</v>
+        <v>3.9668080992002058E-3</v>
       </c>
       <c r="C18">
-        <v>1.1920781821760729E-3</v>
+        <v>3.6709723615703828E-3</v>
       </c>
       <c r="D18">
-        <v>1.76682786963326</v>
+        <v>1.0805878411743941</v>
       </c>
       <c r="E18">
-        <v>7.7257059796373539E-2</v>
+        <v>0.27988049348133942</v>
       </c>
       <c r="F18">
-        <v>-2.3023334877064021E-4</v>
+        <v>-3.2281655177196929E-3</v>
       </c>
       <c r="G18">
-        <v>4.4426272588715234E-3</v>
+        <v>1.116178171612011E-2</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -1788,22 +1788,22 @@
         <v>23</v>
       </c>
       <c r="B19">
-        <v>-4.1282459149529719E-5</v>
+        <v>6.454151646594769E-4</v>
       </c>
       <c r="C19">
-        <v>4.9168465732919546E-4</v>
+        <v>3.0646180847686759E-3</v>
       </c>
       <c r="D19">
-        <v>-8.3961251452859667E-2</v>
+        <v>0.21060215230968801</v>
       </c>
       <c r="E19">
-        <v>0.93308723980494679</v>
+        <v>0.83319773268075525</v>
       </c>
       <c r="F19">
-        <v>-1.004966679265671E-3</v>
+        <v>-5.3611259078572464E-3</v>
       </c>
       <c r="G19">
-        <v>9.2240176096661133E-4</v>
+        <v>6.6519562371762002E-3</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -1811,22 +1811,22 @@
         <v>24</v>
       </c>
       <c r="B20">
-        <v>-6.6116470924782833E-4</v>
+        <v>2.0052375797639239E-3</v>
       </c>
       <c r="C20">
-        <v>1.208410403914578E-3</v>
+        <v>3.0728167661099718E-3</v>
       </c>
       <c r="D20">
-        <v>-0.54713589613762215</v>
+        <v>0.65257310552312942</v>
       </c>
       <c r="E20">
-        <v>0.58428537259979474</v>
+        <v>0.51403152867710222</v>
       </c>
       <c r="F20">
-        <v>-3.0296055794638999E-3</v>
+        <v>-4.0173726129024614E-3</v>
       </c>
       <c r="G20">
-        <v>1.7072761609682431E-3</v>
+        <v>8.0278477724303084E-3</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -1834,22 +1834,22 @@
         <v>25</v>
       </c>
       <c r="B21">
-        <v>0.64433535288608135</v>
+        <v>0.63526082396039074</v>
       </c>
       <c r="C21">
-        <v>6.2190394812533363E-2</v>
+        <v>0.1025473305900703</v>
       </c>
       <c r="D21">
-        <v>10.3606892162104</v>
+        <v>6.1948060500943312</v>
       </c>
       <c r="E21">
-        <v>3.7425546628400569E-25</v>
+        <v>5.8356844062799279E-10</v>
       </c>
       <c r="F21">
-        <v>0.52244441886918935</v>
+        <v>0.43427174929313039</v>
       </c>
       <c r="G21">
-        <v>0.76622628690297334</v>
+        <v>0.83624989862765098</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -1857,22 +1857,22 @@
         <v>26</v>
       </c>
       <c r="B22">
-        <v>7.3568471290819393E-3</v>
+        <v>0.34006420712551</v>
       </c>
       <c r="C22">
-        <v>9.8051263969754138E-2</v>
+        <v>0.10754522896031821</v>
       </c>
       <c r="D22">
-        <v>7.5030620016803717E-2</v>
+        <v>3.162057586496803</v>
       </c>
       <c r="E22">
-        <v>0.94019034929985124</v>
+        <v>1.5665858087019521E-3</v>
       </c>
       <c r="F22">
-        <v>-0.18482009889026599</v>
+        <v>0.12927943165417219</v>
       </c>
       <c r="G22">
-        <v>0.19953379314842989</v>
+        <v>0.55084898259684778</v>
       </c>
     </row>
   </sheetData>
@@ -1911,22 +1911,22 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>-8.3944566695275439E-4</v>
+        <v>1.710370914977169E-2</v>
       </c>
       <c r="C2">
-        <v>1.402970452714305E-3</v>
+        <v>9.0208295326111819E-3</v>
       </c>
       <c r="D2">
-        <v>-0.59833453037353146</v>
+        <v>1.896023984040504</v>
       </c>
       <c r="E2">
-        <v>0.54961674065808153</v>
+        <v>5.7956873146974681E-2</v>
       </c>
       <c r="F2">
-        <v>-3.5892172256466472E-3</v>
+        <v>-5.7679184482151494E-4</v>
       </c>
       <c r="G2">
-        <v>1.910325891741138E-3</v>
+        <v>3.4784210144364891E-2</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -1934,22 +1934,22 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>4.2333570046789804E-3</v>
+        <v>-3.9905604641714831E-3</v>
       </c>
       <c r="C3">
-        <v>1.013434924571909E-3</v>
+        <v>4.8890590339567943E-3</v>
       </c>
       <c r="D3">
-        <v>4.1772361520570422</v>
+        <v>-0.81622259752954107</v>
       </c>
       <c r="E3">
-        <v>2.9507263298109831E-5</v>
+        <v>0.41437283461101559</v>
       </c>
       <c r="F3">
-        <v>2.247061051842972E-3</v>
+        <v>-1.357294008901699E-2</v>
       </c>
       <c r="G3">
-        <v>6.2196529575149883E-3</v>
+        <v>5.5918191606740223E-3</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -1957,22 +1957,22 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>2.214922611447939E-3</v>
+        <v>-4.1405802762364656E-3</v>
       </c>
       <c r="C4">
-        <v>6.9058571131661137E-4</v>
+        <v>3.4951867801749021E-3</v>
       </c>
       <c r="D4">
-        <v>3.2073102225430619</v>
+        <v>-1.1846520763131489</v>
       </c>
       <c r="E4">
-        <v>1.339824282966048E-3</v>
+        <v>0.23615503789758291</v>
       </c>
       <c r="F4">
-        <v>8.6139948902940627E-4</v>
+        <v>-1.0991020484619789E-2</v>
       </c>
       <c r="G4">
-        <v>3.5684457338664732E-3</v>
+        <v>2.709859932146856E-3</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -1980,22 +1980,22 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>5.1542436819341413E-3</v>
+        <v>-2.4778685128157558E-3</v>
       </c>
       <c r="C5">
-        <v>1.6413877790694329E-3</v>
+        <v>2.5055627169051019E-3</v>
       </c>
       <c r="D5">
-        <v>3.1401742767064369</v>
+        <v>-0.98894691244306421</v>
       </c>
       <c r="E5">
-        <v>1.688473556134673E-3</v>
+        <v>0.32268911621188312</v>
       </c>
       <c r="F5">
-        <v>1.9371827502938661E-3</v>
+        <v>-7.3886811989560836E-3</v>
       </c>
       <c r="G5">
-        <v>8.3713046135744165E-3</v>
+        <v>2.432944173324572E-3</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -2003,22 +2003,22 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>-1.9272437352925299E-3</v>
+        <v>-2.6155330176706459E-3</v>
       </c>
       <c r="C6">
-        <v>3.481470706827877E-3</v>
+        <v>2.243770950151598E-3</v>
       </c>
       <c r="D6">
-        <v>-0.55357172229334306</v>
+        <v>-1.165686282503092</v>
       </c>
       <c r="E6">
-        <v>0.57987198303009424</v>
+        <v>0.24374130830667989</v>
       </c>
       <c r="F6">
-        <v>-8.7508009339063737E-3</v>
+        <v>-7.0132432695249941E-3</v>
       </c>
       <c r="G6">
-        <v>4.896313463321313E-3</v>
+        <v>1.782177234183702E-3</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -2026,22 +2026,22 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>-2.057740684568322E-4</v>
+        <v>-1.5751438680498969E-3</v>
       </c>
       <c r="C7">
-        <v>3.0450346515892169E-3</v>
+        <v>2.4979385029444512E-3</v>
       </c>
       <c r="D7">
-        <v>-6.7576921776386953E-2</v>
+        <v>-0.63057752070084694</v>
       </c>
       <c r="E7">
-        <v>0.94612242714842887</v>
+        <v>0.52831680085019417</v>
       </c>
       <c r="F7">
-        <v>-6.1739323172481687E-3</v>
+        <v>-6.4710133694169201E-3</v>
       </c>
       <c r="G7">
-        <v>5.7623841803345049E-3</v>
+        <v>3.3207256333171258E-3</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -2049,22 +2049,22 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>2.4416650818594139E-4</v>
+        <v>3.4127068497205319E-3</v>
       </c>
       <c r="C8">
-        <v>3.3817780070002721E-3</v>
+        <v>3.1208942055893792E-3</v>
       </c>
       <c r="D8">
-        <v>7.2200631644217153E-2</v>
+        <v>1.0935028952947301</v>
       </c>
       <c r="E8">
-        <v>0.94244224250808828</v>
+        <v>0.27417305848246309</v>
       </c>
       <c r="F8">
-        <v>-6.3839965892442344E-3</v>
+        <v>-2.7041333927943952E-3</v>
       </c>
       <c r="G8">
-        <v>6.872329605616118E-3</v>
+        <v>9.5295470922354582E-3</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
@@ -2072,22 +2072,22 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>-6.930952494170672E-4</v>
+        <v>5.2456731113296054E-3</v>
       </c>
       <c r="C9">
-        <v>3.6969453510142859E-3</v>
+        <v>6.8189752410497042E-3</v>
       </c>
       <c r="D9">
-        <v>-0.1874778184716501</v>
+        <v>0.76927587003851516</v>
       </c>
       <c r="E9">
-        <v>0.85128601363881184</v>
+        <v>0.44172955872025199</v>
       </c>
       <c r="F9">
-        <v>-7.938974990217857E-3</v>
+        <v>-8.1192727725981489E-3</v>
       </c>
       <c r="G9">
-        <v>6.5527844913837218E-3</v>
+        <v>1.8610618995257362E-2</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -2095,22 +2095,22 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>-5.1628439420491039E-3</v>
+        <v>1.7557267557755111E-5</v>
       </c>
       <c r="C10">
-        <v>3.9197892151119759E-3</v>
+        <v>2.3013519393751299E-3</v>
       </c>
       <c r="D10">
-        <v>-1.317122849908555</v>
+        <v>7.6291102014246059E-3</v>
       </c>
       <c r="E10">
-        <v>0.1877974489318556</v>
+        <v>0.99391290980582248</v>
       </c>
       <c r="F10">
-        <v>-1.2845489630657099E-2</v>
+        <v>-4.4930096493689059E-3</v>
       </c>
       <c r="G10">
-        <v>2.5198017465588962E-3</v>
+        <v>4.5281241844844161E-3</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -2118,22 +2118,22 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>-2.7330214601104419E-3</v>
+        <v>-3.7029379406339209E-3</v>
       </c>
       <c r="C11">
-        <v>2.0190888278806499E-3</v>
+        <v>2.1195533475255159E-3</v>
       </c>
       <c r="D11">
-        <v>-1.353591492544276</v>
+        <v>-1.7470369146202129</v>
       </c>
       <c r="E11">
-        <v>0.17586674260536361</v>
+        <v>8.0630935026990272E-2</v>
       </c>
       <c r="F11">
-        <v>-6.6903628443437096E-3</v>
+        <v>-7.8571861650952417E-3</v>
       </c>
       <c r="G11">
-        <v>1.2243199241228249E-3</v>
+        <v>4.5131028382739899E-4</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -2141,22 +2141,22 @@
         <v>16</v>
       </c>
       <c r="B12">
-        <v>-6.8463158372724644E-3</v>
+        <v>3.1408621718328013E-2</v>
       </c>
       <c r="C12">
-        <v>8.7137766843701191E-3</v>
+        <v>2.1394953593598189E-2</v>
       </c>
       <c r="D12">
-        <v>-0.78568869564361044</v>
+        <v>1.4680387868532749</v>
       </c>
       <c r="E12">
-        <v>0.43204988749731521</v>
+        <v>0.1420936874171175</v>
       </c>
       <c r="F12">
-        <v>-2.3925004307962749E-2</v>
+        <v>-1.052471677603025E-2</v>
       </c>
       <c r="G12">
-        <v>1.023237263341782E-2</v>
+        <v>7.3341960212686269E-2</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -2164,22 +2164,22 @@
         <v>17</v>
       </c>
       <c r="B13">
-        <v>-1.9288814015661841E-3</v>
+        <v>1.258617116299832E-2</v>
       </c>
       <c r="C13">
-        <v>5.3039508101767798E-3</v>
+        <v>1.0546061588250191E-2</v>
       </c>
       <c r="D13">
-        <v>-0.36366879531861551</v>
+        <v>1.19344753087931</v>
       </c>
       <c r="E13">
-        <v>0.71610534778738621</v>
+        <v>0.23269414947709929</v>
       </c>
       <c r="F13">
-        <v>-1.2324433965284711E-2</v>
+        <v>-8.083729728713334E-3</v>
       </c>
       <c r="G13">
-        <v>8.4666711621523456E-3</v>
+        <v>3.325607205470997E-2</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -2187,22 +2187,22 @@
         <v>18</v>
       </c>
       <c r="B14">
-        <v>-8.3108320770921944E-3</v>
+        <v>-1.323021304388244E-2</v>
       </c>
       <c r="C14">
-        <v>3.7753376927253351E-3</v>
+        <v>9.1928236158325613E-3</v>
       </c>
       <c r="D14">
-        <v>-2.2013479994402259</v>
+        <v>-1.4391892629263969</v>
       </c>
       <c r="E14">
-        <v>2.7711397267351581E-2</v>
+        <v>0.15009690666455611</v>
       </c>
       <c r="F14">
-        <v>-1.5710357984310391E-2</v>
+        <v>-3.1247816247143539E-2</v>
       </c>
       <c r="G14">
-        <v>-9.1130616987399309E-4</v>
+        <v>4.7873901593786516E-3</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
@@ -2210,22 +2210,22 @@
         <v>19</v>
       </c>
       <c r="B15">
-        <v>1.8000721393001799E-2</v>
+        <v>-3.8606073727684852E-3</v>
       </c>
       <c r="C15">
-        <v>1.774260883933242E-2</v>
+        <v>5.6476496212455899E-3</v>
       </c>
       <c r="D15">
-        <v>1.014547609993925</v>
+        <v>-0.68357770606828605</v>
       </c>
       <c r="E15">
-        <v>0.31032152358127718</v>
+        <v>0.49424186638409362</v>
       </c>
       <c r="F15">
-        <v>-1.6774152923871761E-2</v>
+        <v>-1.4929797227711121E-2</v>
       </c>
       <c r="G15">
-        <v>5.2775595709875361E-2</v>
+        <v>7.2085824821741494E-3</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
@@ -2233,22 +2233,22 @@
         <v>20</v>
       </c>
       <c r="B16">
-        <v>9.689406030787993E-3</v>
+        <v>-1.25576583314746E-4</v>
       </c>
       <c r="C16">
-        <v>7.5605167331636346E-3</v>
+        <v>2.3734403294049448E-3</v>
       </c>
       <c r="D16">
-        <v>1.2815798671916361</v>
+        <v>-5.2909096453345343E-2</v>
       </c>
       <c r="E16">
-        <v>0.19999006639645719</v>
+        <v>0.95780433662821118</v>
       </c>
       <c r="F16">
-        <v>-5.1289344707251584E-3</v>
+        <v>-4.7774341484033197E-3</v>
       </c>
       <c r="G16">
-        <v>2.4507746532301141E-2</v>
+        <v>4.5262809817738277E-3</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -2256,22 +2256,22 @@
         <v>21</v>
       </c>
       <c r="B17">
-        <v>-8.9830933759924708E-3</v>
+        <v>-1.840547887137389E-3</v>
       </c>
       <c r="C17">
-        <v>8.7070245151720654E-3</v>
+        <v>2.256999160851291E-3</v>
       </c>
       <c r="D17">
-        <v>-1.031706452685341</v>
+        <v>-0.81548452434655516</v>
       </c>
       <c r="E17">
-        <v>0.3022096536737281</v>
+        <v>0.41479501940006752</v>
       </c>
       <c r="F17">
-        <v>-2.6048547838237041E-2</v>
+        <v>-6.2641849555430439E-3</v>
       </c>
       <c r="G17">
-        <v>8.0823610862521024E-3</v>
+        <v>2.5830891812682649E-3</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -2279,22 +2279,22 @@
         <v>22</v>
       </c>
       <c r="B18">
-        <v>2.0160570750421898E-3</v>
+        <v>-1.031042035708196E-3</v>
       </c>
       <c r="C18">
-        <v>1.815567803035618E-3</v>
+        <v>2.0483631948130152E-3</v>
       </c>
       <c r="D18">
-        <v>1.110427862661673</v>
+        <v>-0.5033492294330717</v>
       </c>
       <c r="E18">
-        <v>0.26681469726094947</v>
+        <v>0.61471876026194017</v>
       </c>
       <c r="F18">
-        <v>-1.542390430398131E-3</v>
+        <v>-5.0457601247991084E-3</v>
       </c>
       <c r="G18">
-        <v>5.5745045804825111E-3</v>
+        <v>2.983676053382716E-3</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -2302,22 +2302,22 @@
         <v>23</v>
       </c>
       <c r="B19">
-        <v>1.5061896239392889E-3</v>
+        <v>-4.4514458553369376E-3</v>
       </c>
       <c r="C19">
-        <v>5.8173565042256628E-4</v>
+        <v>2.9326471535353719E-3</v>
       </c>
       <c r="D19">
-        <v>2.589130686498601</v>
+        <v>-1.5178934328906979</v>
       </c>
       <c r="E19">
-        <v>9.6218570618795997E-3</v>
+        <v>0.12904126576395161</v>
       </c>
       <c r="F19">
-        <v>3.660087005880764E-4</v>
+        <v>-1.0199328655630171E-2</v>
       </c>
       <c r="G19">
-        <v>2.6463705472905019E-3</v>
+        <v>1.296436944956297E-3</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -2325,22 +2325,22 @@
         <v>24</v>
       </c>
       <c r="B20">
-        <v>3.8207062681002232E-4</v>
+        <v>-4.3905467502790294E-3</v>
       </c>
       <c r="C20">
-        <v>2.503258782559711E-3</v>
+        <v>2.860027804382625E-3</v>
       </c>
       <c r="D20">
-        <v>0.15262929644826231</v>
+        <v>-1.535141282036167</v>
       </c>
       <c r="E20">
-        <v>0.87869062045499124</v>
+        <v>0.12474912782400401</v>
       </c>
       <c r="F20">
-        <v>-4.5242264309905949E-3</v>
+        <v>-9.9960982416521411E-3</v>
       </c>
       <c r="G20">
-        <v>5.2883676846106394E-3</v>
+        <v>1.2150047410940841E-3</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -2348,22 +2348,22 @@
         <v>25</v>
       </c>
       <c r="B21">
-        <v>0.61935836042663062</v>
+        <v>0.68001143039902401</v>
       </c>
       <c r="C21">
-        <v>0.14831833501373001</v>
+        <v>8.4857479989765866E-2</v>
       </c>
       <c r="D21">
-        <v>4.1758718527233736</v>
+        <v>8.0135708776767345</v>
       </c>
       <c r="E21">
-        <v>2.9684690394740548E-5</v>
+        <v>1.11425002547203E-15</v>
       </c>
       <c r="F21">
-        <v>0.32865976555277382</v>
+        <v>0.51369382580025458</v>
       </c>
       <c r="G21">
-        <v>0.91005695530048747</v>
+        <v>0.84632903499779344</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -2371,22 +2371,22 @@
         <v>26</v>
       </c>
       <c r="B22">
-        <v>7.3226748651817025E-2</v>
+        <v>0.29150778841341879</v>
       </c>
       <c r="C22">
-        <v>0.1150878343889675</v>
+        <v>8.6677154995236441E-2</v>
       </c>
       <c r="D22">
-        <v>0.63626836876892912</v>
+        <v>3.3631443998068389</v>
       </c>
       <c r="E22">
-        <v>0.52460151801601274</v>
+        <v>7.7060044198277024E-4</v>
       </c>
       <c r="F22">
-        <v>-0.1523412618092696</v>
+        <v>0.1216236863403594</v>
       </c>
       <c r="G22">
-        <v>0.29879475911290371</v>
+        <v>0.46139189048647827</v>
       </c>
     </row>
   </sheetData>
@@ -2424,22 +2424,22 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>3.2982685768637691E-4</v>
+        <v>5.2223689578905573E-2</v>
       </c>
       <c r="C2">
-        <v>7.1823272237161897E-4</v>
+        <v>3.2164661203172948E-2</v>
       </c>
       <c r="D2">
-        <v>0.4592200374793311</v>
+        <v>1.6236356182652361</v>
       </c>
       <c r="E2">
-        <v>0.64607616283882607</v>
+        <v>0.1044535989906798</v>
       </c>
       <c r="F2">
-        <v>-1.077883410680152E-3</v>
+        <v>-1.0817887954246191E-2</v>
       </c>
       <c r="G2">
-        <v>1.7375371260529059E-3</v>
+        <v>0.1152652671120573</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -2447,22 +2447,22 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>-1.052122224587909E-3</v>
+        <v>7.3314227375472357E-3</v>
       </c>
       <c r="C3">
-        <v>7.9489971303006832E-4</v>
+        <v>5.3563878798679639E-3</v>
       </c>
       <c r="D3">
-        <v>-1.3235911490989689</v>
+        <v>1.3687251375320411</v>
       </c>
       <c r="E3">
-        <v>0.18563886625585019</v>
+        <v>0.1710852095612494</v>
       </c>
       <c r="F3">
-        <v>-2.6100970334480668E-3</v>
+        <v>-3.16690459422083E-3</v>
       </c>
       <c r="G3">
-        <v>5.058525842722495E-4</v>
+        <v>1.7829750069315298E-2</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -2470,22 +2470,22 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>-4.2658631982008481E-4</v>
+        <v>6.8261167585922794E-3</v>
       </c>
       <c r="C4">
-        <v>6.4330895596363777E-4</v>
+        <v>5.7792058997425139E-3</v>
       </c>
       <c r="D4">
-        <v>-0.66311267061576096</v>
+        <v>1.1811513341126001</v>
       </c>
       <c r="E4">
-        <v>0.50725839627254188</v>
+        <v>0.2375426101407698</v>
       </c>
       <c r="F4">
-        <v>-1.6874487044408781E-3</v>
+        <v>-4.5009186641444456E-3</v>
       </c>
       <c r="G4">
-        <v>8.3427606480070897E-4</v>
+        <v>1.815315218132901E-2</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -2493,22 +2493,22 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>1.044266263829119E-3</v>
+        <v>6.7791528354881484E-3</v>
       </c>
       <c r="C5">
-        <v>4.516984877201388E-4</v>
+        <v>6.281655985229056E-3</v>
       </c>
       <c r="D5">
-        <v>2.311865751642987</v>
+        <v>1.0791983597046579</v>
       </c>
       <c r="E5">
-        <v>2.0785082597816751E-2</v>
+        <v>0.28049931074672269</v>
       </c>
       <c r="F5">
-        <v>1.5895349602643949E-4</v>
+        <v>-5.5326666588312728E-3</v>
       </c>
       <c r="G5">
-        <v>1.929579031631799E-3</v>
+        <v>1.9090972329807571E-2</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -2516,22 +2516,22 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>1.0378641568202941E-3</v>
+        <v>5.3604973695031066E-3</v>
       </c>
       <c r="C6">
-        <v>1.800380735159008E-3</v>
+        <v>6.4050573865947341E-3</v>
       </c>
       <c r="D6">
-        <v>0.57646926372417051</v>
+        <v>0.83691636873108954</v>
       </c>
       <c r="E6">
-        <v>0.56429803935056744</v>
+        <v>0.40263957880408707</v>
       </c>
       <c r="F6">
-        <v>-2.490817242551107E-3</v>
+        <v>-7.1931844271348137E-3</v>
       </c>
       <c r="G6">
-        <v>4.5665455561916951E-3</v>
+        <v>1.791417916614103E-2</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -2539,22 +2539,22 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>1.085300476845898E-3</v>
+        <v>9.7769709432160012E-3</v>
       </c>
       <c r="C7">
-        <v>1.852372813471429E-3</v>
+        <v>8.6257016009051932E-3</v>
       </c>
       <c r="D7">
-        <v>0.58589743325588806</v>
+        <v>1.133469646363606</v>
       </c>
       <c r="E7">
-        <v>0.55794444228853601</v>
+        <v>0.25701708099501569</v>
       </c>
       <c r="F7">
-        <v>-2.5452835234992342E-3</v>
+        <v>-7.1290935359476643E-3</v>
       </c>
       <c r="G7">
-        <v>4.7158844771910298E-3</v>
+        <v>2.668303542237967E-2</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -2562,22 +2562,22 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>2.343613346380116E-3</v>
+        <v>8.6413108049633244E-3</v>
       </c>
       <c r="C8">
-        <v>1.793945788559014E-3</v>
+        <v>7.5420610626507952E-3</v>
       </c>
       <c r="D8">
-        <v>1.30640143159656</v>
+        <v>1.1457492498643569</v>
       </c>
       <c r="E8">
-        <v>0.19141607926919399</v>
+        <v>0.25189891940082437</v>
       </c>
       <c r="F8">
-        <v>-1.1724557894128591E-3</v>
+        <v>-6.1408572470341219E-3</v>
       </c>
       <c r="G8">
-        <v>5.8596824821730911E-3</v>
+        <v>2.3423478856960771E-2</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
@@ -2585,22 +2585,22 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>1.452646296493175E-3</v>
+        <v>9.8511291543039448E-4</v>
       </c>
       <c r="C9">
-        <v>1.3420447259078561E-3</v>
+        <v>9.6627227927092562E-3</v>
       </c>
       <c r="D9">
-        <v>1.0824127307012821</v>
+        <v>0.10194982683076501</v>
       </c>
       <c r="E9">
-        <v>0.27906917395455388</v>
+        <v>0.91879649987602285</v>
       </c>
       <c r="F9">
-        <v>-1.177713031928151E-3</v>
+        <v>-1.795347575087404E-2</v>
       </c>
       <c r="G9">
-        <v>4.083005624914501E-3</v>
+        <v>1.9923701581734829E-2</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -2608,22 +2608,22 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>5.4755155302929938E-3</v>
+        <v>2.9354069856116489E-3</v>
       </c>
       <c r="C10">
-        <v>4.202684577548116E-3</v>
+        <v>3.174832692071047E-3</v>
       </c>
       <c r="D10">
-        <v>1.302861404242585</v>
+        <v>0.92458635472119544</v>
       </c>
       <c r="E10">
-        <v>0.1926220826478727</v>
+        <v>0.35518111355815768</v>
       </c>
       <c r="F10">
-        <v>-2.761594880083245E-3</v>
+        <v>-3.287150747787947E-3</v>
       </c>
       <c r="G10">
-        <v>1.3712625940669231E-2</v>
+        <v>9.1579647190112457E-3</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -2631,22 +2631,22 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>5.2646437427134448E-3</v>
+        <v>7.2881691278494504E-3</v>
       </c>
       <c r="C11">
-        <v>3.1931806042018659E-3</v>
+        <v>8.3216472570443786E-3</v>
       </c>
       <c r="D11">
-        <v>1.6487146814639191</v>
+        <v>0.87580846708924409</v>
       </c>
       <c r="E11">
-        <v>9.9206100959343402E-2</v>
+        <v>0.38113416628371161</v>
       </c>
       <c r="F11">
-        <v>-9.9387523765406219E-4</v>
+        <v>-9.0219597880040608E-3</v>
       </c>
       <c r="G11">
-        <v>1.1523162723080949E-2</v>
+        <v>2.3598298043702962E-2</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -2654,22 +2654,22 @@
         <v>16</v>
       </c>
       <c r="B12">
-        <v>-8.2271234325381358E-4</v>
+        <v>-2.1837882553639051E-2</v>
       </c>
       <c r="C12">
-        <v>4.0372696292262106E-3</v>
+        <v>1.6991867915885951E-2</v>
       </c>
       <c r="D12">
-        <v>-0.2037793902339626</v>
+        <v>-1.2851961103830429</v>
       </c>
       <c r="E12">
-        <v>0.83852589911010211</v>
+        <v>0.1987237625125646</v>
       </c>
       <c r="F12">
-        <v>-8.7356154124145647E-3</v>
+        <v>-5.5141331698837177E-2</v>
       </c>
       <c r="G12">
-        <v>7.0901907259069367E-3</v>
+        <v>1.1465566591559079E-2</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -2677,22 +2677,22 @@
         <v>17</v>
       </c>
       <c r="B13">
-        <v>3.7215599279240988E-3</v>
+        <v>2.3957314312022669E-3</v>
       </c>
       <c r="C13">
-        <v>1.910569192149012E-3</v>
+        <v>3.1869623320345962E-3</v>
       </c>
       <c r="D13">
-        <v>1.947880214554323</v>
+        <v>0.75172881935909242</v>
       </c>
       <c r="E13">
-        <v>5.1429297741904863E-2</v>
+        <v>0.45221415556869871</v>
       </c>
       <c r="F13">
-        <v>-2.3086878659751581E-5</v>
+        <v>-3.850599959671323E-3</v>
       </c>
       <c r="G13">
-        <v>7.4662067345079488E-3</v>
+        <v>8.642062822075856E-3</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -2700,22 +2700,22 @@
         <v>18</v>
       </c>
       <c r="B14">
-        <v>5.6750582093016578E-3</v>
+        <v>-3.1078624423292729E-3</v>
       </c>
       <c r="C14">
-        <v>4.1840112808437576E-3</v>
+        <v>2.82167684715626E-3</v>
       </c>
       <c r="D14">
-        <v>1.3563678079178629</v>
+        <v>-1.101423944227149</v>
       </c>
       <c r="E14">
-        <v>0.1749821706055997</v>
+        <v>0.27071218904176908</v>
       </c>
       <c r="F14">
-        <v>-2.5254532120614088E-3</v>
+        <v>-8.6382474387660738E-3</v>
       </c>
       <c r="G14">
-        <v>1.3875569630664719E-2</v>
+        <v>2.4225225541075271E-3</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
@@ -2723,22 +2723,22 @@
         <v>19</v>
       </c>
       <c r="B15">
-        <v>-1.717601526038769E-2</v>
+        <v>1.0996626082112051E-3</v>
       </c>
       <c r="C15">
-        <v>1.445830682828401E-2</v>
+        <v>2.760074769787433E-3</v>
       </c>
       <c r="D15">
-        <v>-1.1879686511277501</v>
+        <v>0.39841768790049681</v>
       </c>
       <c r="E15">
-        <v>0.23484576065395449</v>
+        <v>0.69032232178528619</v>
       </c>
       <c r="F15">
-        <v>-4.5513775921253892E-2</v>
+        <v>-4.3099845352098454E-3</v>
       </c>
       <c r="G15">
-        <v>1.11617454004785E-2</v>
+        <v>6.5093097516322543E-3</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
@@ -2746,22 +2746,22 @@
         <v>20</v>
       </c>
       <c r="B16">
-        <v>6.8074149357354435E-4</v>
+        <v>1.590391981958775E-3</v>
       </c>
       <c r="C16">
-        <v>1.4339344554078831E-3</v>
+        <v>2.984706889913244E-3</v>
       </c>
       <c r="D16">
-        <v>0.47473682706083481</v>
+        <v>0.53284695637399837</v>
       </c>
       <c r="E16">
-        <v>0.63497456540027708</v>
+        <v>0.59413952613933674</v>
       </c>
       <c r="F16">
-        <v>-2.1297183952169621E-3</v>
+        <v>-4.2595260266797396E-3</v>
       </c>
       <c r="G16">
-        <v>3.4912013823640512E-3</v>
+        <v>7.4403099905972899E-3</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -2769,22 +2769,22 @@
         <v>21</v>
       </c>
       <c r="B17">
-        <v>-5.7320227083414287E-3</v>
+        <v>1.610830547688513E-3</v>
       </c>
       <c r="C17">
-        <v>4.5325224801461136E-3</v>
+        <v>2.9551522223862851E-3</v>
       </c>
       <c r="D17">
-        <v>-1.264642973851648</v>
+        <v>0.54509224109875731</v>
       </c>
       <c r="E17">
-        <v>0.20599934076118179</v>
+        <v>0.58569007873950962</v>
       </c>
       <c r="F17">
-        <v>-1.4615603528545979E-2</v>
+        <v>-4.1811613770221046E-3</v>
       </c>
       <c r="G17">
-        <v>3.1515581118631182E-3</v>
+        <v>7.4028224723991318E-3</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -2792,22 +2792,22 @@
         <v>22</v>
       </c>
       <c r="B18">
-        <v>2.3355452534176661E-4</v>
+        <v>2.354717404798395E-3</v>
       </c>
       <c r="C18">
-        <v>1.150443762786715E-3</v>
+        <v>3.1026861783778671E-3</v>
       </c>
       <c r="D18">
-        <v>0.20301255297871179</v>
+        <v>0.75892864099761403</v>
       </c>
       <c r="E18">
-        <v>0.83912522065599404</v>
+        <v>0.44789524482544091</v>
       </c>
       <c r="F18">
-        <v>-2.0212738159589372E-3</v>
+        <v>-3.726435760152442E-3</v>
       </c>
       <c r="G18">
-        <v>2.4883828666424699E-3</v>
+        <v>8.435870569749232E-3</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -2815,22 +2815,22 @@
         <v>23</v>
       </c>
       <c r="B19">
-        <v>-7.9434629389777789E-5</v>
+        <v>8.3220939487459178E-4</v>
       </c>
       <c r="C19">
-        <v>1.048858277388818E-3</v>
+        <v>3.2240252404739942E-3</v>
       </c>
       <c r="D19">
-        <v>-7.5734378134988831E-2</v>
+        <v>0.25812744404948917</v>
       </c>
       <c r="E19">
-        <v>0.93963042472815961</v>
+        <v>0.79630855180532922</v>
       </c>
       <c r="F19">
-        <v>-2.1351590779585838E-3</v>
+        <v>-5.4867639617025227E-3</v>
       </c>
       <c r="G19">
-        <v>1.976289819179028E-3</v>
+        <v>7.1511827514517063E-3</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -2838,22 +2838,22 @@
         <v>24</v>
       </c>
       <c r="B20">
-        <v>-2.0117264109952571E-3</v>
+        <v>1.574104123747463E-3</v>
       </c>
       <c r="C20">
-        <v>6.160394421172628E-4</v>
+        <v>3.0402379939262242E-3</v>
       </c>
       <c r="D20">
-        <v>-3.2655805350403622</v>
+        <v>0.51775687524864911</v>
       </c>
       <c r="E20">
-        <v>1.09239936987926E-3</v>
+        <v>0.6046279103069081</v>
       </c>
       <c r="F20">
-        <v>-3.2191415306012392E-3</v>
+        <v>-4.3846528487782397E-3</v>
       </c>
       <c r="G20">
-        <v>-8.0431129138927473E-4</v>
+        <v>7.5328610962731666E-3</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -2861,22 +2861,22 @@
         <v>25</v>
       </c>
       <c r="B21">
-        <v>0.72198869096569984</v>
+        <v>0.71777444814448144</v>
       </c>
       <c r="C21">
-        <v>6.3732488827104028E-2</v>
+        <v>9.2182409301726623E-2</v>
       </c>
       <c r="D21">
-        <v>11.3284245484958</v>
+        <v>7.7864578891087541</v>
       </c>
       <c r="E21">
-        <v>9.4896250038420854E-30</v>
+        <v>6.8913874622219622E-15</v>
       </c>
       <c r="F21">
-        <v>0.59707530821947452</v>
+        <v>0.53710024590496719</v>
       </c>
       <c r="G21">
-        <v>0.84690207371192516</v>
+        <v>0.89844865038399568</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -2884,22 +2884,22 @@
         <v>26</v>
       </c>
       <c r="B22">
-        <v>-6.1467510156875099E-2</v>
+        <v>0.12419838053646649</v>
       </c>
       <c r="C22">
-        <v>5.0695839632399493E-2</v>
+        <v>3.058707346905495E-2</v>
       </c>
       <c r="D22">
-        <v>-1.212476420206906</v>
+        <v>4.0604858997745712</v>
       </c>
       <c r="E22">
-        <v>0.2253300634091695</v>
+        <v>4.8970694792474558E-5</v>
       </c>
       <c r="F22">
-        <v>-0.16082953000239639</v>
+        <v>6.4248818144638176E-2</v>
       </c>
       <c r="G22">
-        <v>3.7894509688646189E-2</v>
+        <v>0.18414794292829481</v>
       </c>
     </row>
   </sheetData>
@@ -2937,22 +2937,22 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>4.729214129688991E-4</v>
+        <v>3.971440364486703E-2</v>
       </c>
       <c r="C2">
-        <v>1.039402531923595E-3</v>
+        <v>3.2309472294348107E-2</v>
       </c>
       <c r="D2">
-        <v>0.45499351641339192</v>
+        <v>1.2291876290351631</v>
       </c>
       <c r="E2">
-        <v>0.64911390329307439</v>
+        <v>0.21900146608856641</v>
       </c>
       <c r="F2">
-        <v>-1.5642701150410899E-3</v>
+        <v>-2.3610998411549969E-2</v>
       </c>
       <c r="G2">
-        <v>2.5101129409788878E-3</v>
+        <v>0.103039805701284</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -2960,22 +2960,22 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>-1.489822098851305E-3</v>
+        <v>6.032841628165142E-3</v>
       </c>
       <c r="C3">
-        <v>1.6776035996864821E-3</v>
+        <v>7.4049662414271914E-3</v>
       </c>
       <c r="D3">
-        <v>-0.88806563071856182</v>
+        <v>0.81470211091771383</v>
       </c>
       <c r="E3">
-        <v>0.37450544889693699</v>
+        <v>0.41524284477252121</v>
       </c>
       <c r="F3">
-        <v>-4.7778647345715604E-3</v>
+        <v>-8.4806255117670839E-3</v>
       </c>
       <c r="G3">
-        <v>1.79822053686895E-3</v>
+        <v>2.054630876809737E-2</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -2983,22 +2983,22 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>3.9105773468882859E-4</v>
+        <v>8.4376926396964036E-3</v>
       </c>
       <c r="C4">
-        <v>2.7371361302777988E-4</v>
+        <v>6.8798717862596209E-3</v>
       </c>
       <c r="D4">
-        <v>1.4287113102012181</v>
+        <v>1.226431669344193</v>
       </c>
       <c r="E4">
-        <v>0.1530872256802642</v>
+        <v>0.22003627446680099</v>
       </c>
       <c r="F4">
-        <v>-1.4541108892395329E-4</v>
+        <v>-5.0466082796257021E-3</v>
       </c>
       <c r="G4">
-        <v>9.2752655830161059E-4</v>
+        <v>2.1921993559018509E-2</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -3006,22 +3006,22 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>3.851603677161444E-3</v>
+        <v>9.9093820679684724E-3</v>
       </c>
       <c r="C5">
-        <v>2.8239414347069878E-3</v>
+        <v>6.7219258817941378E-3</v>
       </c>
       <c r="D5">
-        <v>1.3639106072895899</v>
+        <v>1.474187939918727</v>
       </c>
       <c r="E5">
-        <v>0.1725957019750618</v>
+        <v>0.14043099607996071</v>
       </c>
       <c r="F5">
-        <v>-1.683219829314621E-3</v>
+        <v>-3.2653505670956831E-3</v>
       </c>
       <c r="G5">
-        <v>9.386427183637509E-3</v>
+        <v>2.3084114703032631E-2</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -3029,22 +3029,22 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>-4.41224669756756E-3</v>
+        <v>1.072605886748736E-2</v>
       </c>
       <c r="C6">
-        <v>2.131787406813062E-3</v>
+        <v>6.8036720430811994E-3</v>
       </c>
       <c r="D6">
-        <v>-2.06974048325189</v>
+        <v>1.576510272624754</v>
       </c>
       <c r="E6">
-        <v>3.8476653499672983E-2</v>
+        <v>0.1149082532238187</v>
       </c>
       <c r="F6">
-        <v>-8.590473237617198E-3</v>
+        <v>-2.608893299573839E-3</v>
       </c>
       <c r="G6">
-        <v>-2.3402015751792119E-4</v>
+        <v>2.4061011034548552E-2</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -3052,22 +3052,22 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>-2.275156771227711E-3</v>
+        <v>9.4666120318123992E-3</v>
       </c>
       <c r="C7">
-        <v>2.9886667808608669E-3</v>
+        <v>6.7888814024859578E-3</v>
       </c>
       <c r="D7">
-        <v>-0.7612614379754864</v>
+        <v>1.394428841892261</v>
       </c>
       <c r="E7">
-        <v>0.4465009283904473</v>
+        <v>0.16318814359928679</v>
       </c>
       <c r="F7">
-        <v>-8.1328360235062725E-3</v>
+        <v>-3.8393510123738502E-3</v>
       </c>
       <c r="G7">
-        <v>3.5825224810508501E-3</v>
+        <v>2.2772575075998652E-2</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -3075,22 +3075,22 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>-1.449471593713115E-3</v>
+        <v>1.4212592795691471E-2</v>
       </c>
       <c r="C8">
-        <v>3.0417866734928729E-3</v>
+        <v>6.9350496013642557E-3</v>
       </c>
       <c r="D8">
-        <v>-0.47651980539736272</v>
+        <v>2.0493858894528429</v>
       </c>
       <c r="E8">
-        <v>0.6337041008946559</v>
+        <v>4.0424395932017493E-2</v>
       </c>
       <c r="F8">
-        <v>-7.411263922413043E-3</v>
+        <v>6.2014534601866761E-4</v>
       </c>
       <c r="G8">
-        <v>4.512320734986813E-3</v>
+        <v>2.780504024536427E-2</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
@@ -3098,22 +3098,22 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>-5.6900293057926717E-4</v>
+        <v>1.7541769754266221E-2</v>
       </c>
       <c r="C9">
-        <v>2.8635941511893342E-3</v>
+        <v>7.5422677544349226E-3</v>
       </c>
       <c r="D9">
-        <v>-0.1987023651179563</v>
+        <v>2.3257951488067361</v>
       </c>
       <c r="E9">
-        <v>0.84249557382039997</v>
+        <v>2.0029481571676961E-2</v>
       </c>
       <c r="F9">
-        <v>-6.1815443332499066E-3</v>
+        <v>2.7591965938159788E-3</v>
       </c>
       <c r="G9">
-        <v>5.0435384720913731E-3</v>
+        <v>3.2324342914716447E-2</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -3121,22 +3121,22 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>1.6274872424821001E-3</v>
+        <v>1.4371227408967119E-2</v>
       </c>
       <c r="C10">
-        <v>7.0515225583557889E-3</v>
+        <v>8.639931911207285E-3</v>
       </c>
       <c r="D10">
-        <v>0.2307994094911586</v>
+        <v>1.663349613939143</v>
       </c>
       <c r="E10">
-        <v>0.81747064000827452</v>
+        <v>9.624247274405133E-2</v>
       </c>
       <c r="F10">
-        <v>-1.2193243008066989E-2</v>
+        <v>-2.562727965877469E-3</v>
       </c>
       <c r="G10">
-        <v>1.5448217493031191E-2</v>
+        <v>3.1305182783811718E-2</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -3144,22 +3144,22 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>4.5197153854178579E-3</v>
+        <v>1.493260141164165E-2</v>
       </c>
       <c r="C11">
-        <v>4.1062983225033777E-3</v>
+        <v>7.1447538286535661E-3</v>
       </c>
       <c r="D11">
-        <v>1.100678769647317</v>
+        <v>2.0900092249162512</v>
       </c>
       <c r="E11">
-        <v>0.27103648940495939</v>
+        <v>3.6616971041279929E-2</v>
       </c>
       <c r="F11">
-        <v>-3.5284814364660022E-3</v>
+        <v>9.2914122907600434E-4</v>
       </c>
       <c r="G11">
-        <v>1.256791220730172E-2</v>
+        <v>2.8936061594207311E-2</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -3167,22 +3167,22 @@
         <v>16</v>
       </c>
       <c r="B12">
-        <v>8.239032153180139E-3</v>
+        <v>-1.5153174843655639E-3</v>
       </c>
       <c r="C12">
-        <v>5.3295287062565776E-3</v>
+        <v>2.757429722845563E-2</v>
       </c>
       <c r="D12">
-        <v>1.5459213388808579</v>
+        <v>-5.4953983842671188E-2</v>
       </c>
       <c r="E12">
-        <v>0.12212356632913519</v>
+        <v>0.95617512393186976</v>
       </c>
       <c r="F12">
-        <v>-2.2066521656551041E-3</v>
+        <v>-5.5559946951141227E-2</v>
       </c>
       <c r="G12">
-        <v>1.8684716472015379E-2</v>
+        <v>5.25293119824101E-2</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -3190,22 +3190,22 @@
         <v>17</v>
       </c>
       <c r="B13">
-        <v>-7.4703363645899361E-4</v>
+        <v>5.5620699947492303E-3</v>
       </c>
       <c r="C13">
-        <v>5.3515099042358493E-3</v>
+        <v>1.0637629245623949E-2</v>
       </c>
       <c r="D13">
-        <v>-0.13959305874921371</v>
+        <v>0.52286744220168446</v>
       </c>
       <c r="E13">
-        <v>0.88898152523751262</v>
+        <v>0.60106650281280372</v>
       </c>
       <c r="F13">
-        <v>-1.123580031167065E-2</v>
+        <v>-1.5287300207563701E-2</v>
       </c>
       <c r="G13">
-        <v>9.741733038752665E-3</v>
+        <v>2.641144019706216E-2</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -3213,22 +3213,22 @@
         <v>18</v>
       </c>
       <c r="B14">
-        <v>6.1045539334456736E-3</v>
+        <v>-1.778957610479553E-3</v>
       </c>
       <c r="C14">
-        <v>5.5473979270511632E-3</v>
+        <v>7.8920860020791628E-3</v>
       </c>
       <c r="D14">
-        <v>1.100435558025793</v>
+        <v>-0.22541031737501199</v>
       </c>
       <c r="E14">
-        <v>0.2711423928250184</v>
+        <v>0.8216600860602693</v>
       </c>
       <c r="F14">
-        <v>-4.7681462114867604E-3</v>
+        <v>-1.7247161937447419E-2</v>
       </c>
       <c r="G14">
-        <v>1.697725407837811E-2</v>
+        <v>1.368924671648831E-2</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
@@ -3236,22 +3236,22 @@
         <v>19</v>
       </c>
       <c r="B15">
-        <v>-6.5291157932325927E-3</v>
+        <v>7.5522941676666733E-3</v>
       </c>
       <c r="C15">
-        <v>2.0323815913658869E-2</v>
+        <v>6.6343939602688182E-3</v>
       </c>
       <c r="D15">
-        <v>-0.32125442490573941</v>
+        <v>1.1383547936548319</v>
       </c>
       <c r="E15">
-        <v>0.74801759097243847</v>
+        <v>0.25497236257721761</v>
       </c>
       <c r="F15">
-        <v>-4.636306301242598E-2</v>
+        <v>-5.4508790537102694E-3</v>
       </c>
       <c r="G15">
-        <v>3.3304831425960787E-2</v>
+        <v>2.0555467389043621E-2</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
@@ -3259,22 +3259,22 @@
         <v>20</v>
       </c>
       <c r="B16">
-        <v>-2.277845160122909E-3</v>
+        <v>1.1736900104680439E-2</v>
       </c>
       <c r="C16">
-        <v>4.571349422563372E-3</v>
+        <v>6.9503534285761523E-3</v>
       </c>
       <c r="D16">
-        <v>-0.49828725602988672</v>
+        <v>1.6886767306572581</v>
       </c>
       <c r="E16">
-        <v>0.61828158893080098</v>
+        <v>9.128139726518697E-2</v>
       </c>
       <c r="F16">
-        <v>-1.1237525389095089E-2</v>
+        <v>-1.885542295153302E-3</v>
       </c>
       <c r="G16">
-        <v>6.6818350688492732E-3</v>
+        <v>2.535934250451418E-2</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -3282,22 +3282,22 @@
         <v>21</v>
       </c>
       <c r="B17">
-        <v>-1.004687675798289E-2</v>
+        <v>1.127486414339582E-2</v>
       </c>
       <c r="C17">
-        <v>8.4580357461496395E-3</v>
+        <v>7.2348616241002667E-3</v>
       </c>
       <c r="D17">
-        <v>-1.1878498814049749</v>
+        <v>1.558407711052521</v>
       </c>
       <c r="E17">
-        <v>0.2348925582086194</v>
+        <v>0.1191366298630884</v>
       </c>
       <c r="F17">
-        <v>-2.6624322200388541E-2</v>
+        <v>-2.9052040729716671E-3</v>
       </c>
       <c r="G17">
-        <v>6.5305686844227672E-3</v>
+        <v>2.5454932359763299E-2</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -3305,22 +3305,22 @@
         <v>22</v>
       </c>
       <c r="B18">
-        <v>3.6180906808426852E-4</v>
+        <v>1.138085245380221E-2</v>
       </c>
       <c r="C18">
-        <v>2.015054049300879E-3</v>
+        <v>6.5295702839020947E-3</v>
       </c>
       <c r="D18">
-        <v>0.1795530339296843</v>
+        <v>1.742971123514881</v>
       </c>
       <c r="E18">
-        <v>0.85750347881135891</v>
+        <v>8.1338659007437641E-2</v>
       </c>
       <c r="F18">
-        <v>-3.587624295447052E-3</v>
+        <v>-1.416870137168867E-3</v>
       </c>
       <c r="G18">
-        <v>4.3112424316155886E-3</v>
+        <v>2.41785750447733E-2</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -3328,22 +3328,22 @@
         <v>23</v>
       </c>
       <c r="B19">
-        <v>-9.2962229155861326E-4</v>
+        <v>1.3253649106338311E-2</v>
       </c>
       <c r="C19">
-        <v>1.4311893347156051E-3</v>
+        <v>7.5339047154635384E-3</v>
       </c>
       <c r="D19">
-        <v>-0.64954529006697825</v>
+        <v>1.759200521760627</v>
       </c>
       <c r="E19">
-        <v>0.51598598249173033</v>
+        <v>7.8543455684987482E-2</v>
       </c>
       <c r="F19">
-        <v>-3.7347018426590389E-3</v>
+        <v>-1.512532798926713E-3</v>
       </c>
       <c r="G19">
-        <v>1.875457259541813E-3</v>
+        <v>2.8019831011603321E-2</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -3351,22 +3351,22 @@
         <v>24</v>
       </c>
       <c r="B20">
-        <v>-9.920589782464388E-4</v>
+        <v>1.2769592843210159E-2</v>
       </c>
       <c r="C20">
-        <v>2.7099775326631659E-3</v>
+        <v>7.4352803210020451E-3</v>
       </c>
       <c r="D20">
-        <v>-0.36607645867510802</v>
+        <v>1.717432604005604</v>
       </c>
       <c r="E20">
-        <v>0.71430802334791776</v>
+        <v>8.5900158742120675E-2</v>
       </c>
       <c r="F20">
-        <v>-6.3035173411789634E-3</v>
+        <v>-1.803288800913256E-3</v>
       </c>
       <c r="G20">
-        <v>4.3193993846860849E-3</v>
+        <v>2.7342474487333589E-2</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -3374,22 +3374,22 @@
         <v>25</v>
       </c>
       <c r="B21">
-        <v>0.59155075477501406</v>
+        <v>0.66129463434377422</v>
       </c>
       <c r="C21">
-        <v>7.3454692886496614E-2</v>
+        <v>4.7858867162194833E-2</v>
       </c>
       <c r="D21">
-        <v>8.0532738145007006</v>
+        <v>13.817598985421681</v>
       </c>
       <c r="E21">
-        <v>8.0608293296927298E-16</v>
+        <v>1.996175220159279E-43</v>
       </c>
       <c r="F21">
-        <v>0.44758220222203021</v>
+        <v>0.56749297836498569</v>
       </c>
       <c r="G21">
-        <v>0.73551930732799797</v>
+        <v>0.75509629032256276</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -3397,22 +3397,22 @@
         <v>26</v>
       </c>
       <c r="B22">
-        <v>5.1050910285696249E-3</v>
+        <v>0.2704660131219121</v>
       </c>
       <c r="C22">
-        <v>9.8933881915610353E-2</v>
+        <v>7.1767579146735122E-2</v>
       </c>
       <c r="D22">
-        <v>5.1601038286602542E-2</v>
+        <v>3.7686378213889671</v>
       </c>
       <c r="E22">
-        <v>0.95884659201090339</v>
+        <v>1.6414084791313669E-4</v>
       </c>
       <c r="F22">
-        <v>-0.18880175437676519</v>
+        <v>0.12980414273668339</v>
       </c>
       <c r="G22">
-        <v>0.1990119364339045</v>
+        <v>0.41112788350714069</v>
       </c>
     </row>
   </sheetData>
